--- a/results/dwell_e_target_compliance.xlsx
+++ b/results/dwell_e_target_compliance.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TD3_vanilla_extended_ts102</t>
+          <t>RoundRobin_TransformerCapped</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -776,10 +776,10 @@
         <v>50</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.940829311059496</v>
+        <v>0.9924558079648526</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.9372855404663128</v>
+        <v>0.9909650784190758</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.9222313015706408</v>
+        <v>0.9730023681711834</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.9152279077188206</v>
+        <v>0.964691178706947</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -798,43 +798,43 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>26.26872535755381</v>
+        <v>2.694883030310603</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>27.93315644654784</v>
+        <v>3.296713714255332</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.2808003336163167</v>
+        <v>0.0500364942219212</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.2964973797665937</v>
+        <v>0.0606317315632895</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>57.29902873212629</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="T4" s="6" t="n">
-        <v>196.5718736604782</v>
+        <v>99.89981312549872</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>222.7072554452695</v>
+        <v>99.89981312549872</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>out of its training distribution (trained on Dutch durations)</t>
+          <t>recommended operating strategy (round-robin load management, budget = transformer rating)</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RoundRobin_TransformerCapped</t>
+          <t>MPC_TrackingG2V</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -868,65 +868,65 @@
         <v>50</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.9924558079648526</v>
+        <v>0.8888976501799565</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.9909650784190758</v>
+        <v>0.8769163350439934</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.9730023681711834</v>
+        <v>0.871563878043398</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.964691178706947</v>
+        <v>0.8578120199138543</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2.694883030310603</v>
+        <v>47.34946544745704</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3.296713714255332</v>
+        <v>52.03398451724812</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.0500364942219212</v>
+        <v>0.4846105863783625</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.0606317315632895</v>
+        <v>0.531184719180021</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>0</v>
+        <v>3.8051903892718e-05</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="T5" s="6" t="n">
-        <v>99.89981312549872</v>
+        <v>100.0005405900941</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>99.89981312549872</v>
+        <v>100.0005769132799</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -938,19 +938,15 @@
           <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>diagnostic arm added by this brief (budget = transformer rating)</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ChargeAsFastAsPossible</t>
+          <t>Optimal_Oracle_Tracking</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -960,10 +956,10 @@
         <v>50</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.9987851874291384</v>
+        <v>0.9131912328053232</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.9983878291241496</v>
+        <v>0.908197120177652</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -971,54 +967,54 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.9469199181192218</v>
+        <v>0.8951674572775801</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.9366830129844704</v>
+        <v>0.887321049271486</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
+        <v>38.39923998669178</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>40.4674977109501</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.3989355257491345</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.4190397861235397</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.0553331249412169</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0.0650806308099252</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>176.7342879644401</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="T6" s="6" t="n">
-        <v>226.684671389672</v>
+        <v>100.0000780826473</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>253.1990814461407</v>
+        <v>100.0000780826473</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1034,11 +1030,11 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RoundRobin</t>
+          <t>TD3_vanilla_extended_ts102</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -1048,10 +1044,10 @@
         <v>50</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9558407020336256</v>
+        <v>0.940829311059496</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.9514036786770336</v>
+        <v>0.9372855404663128</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1059,21 +1055,21 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.9061713895925836</v>
+        <v>0.9222313015706408</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.8960550921566799</v>
+        <v>0.9152279077188206</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>19.02069610815025</v>
+        <v>26.26872535755381</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>20.74325422801842</v>
+        <v>27.93315644654784</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1081,10 +1077,10 @@
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2354789053525755</v>
+        <v>0.2808003336163167</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2523482662409649</v>
+        <v>0.2964973797665937</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1092,10 +1088,10 @@
         </is>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>70.83023173404438</v>
+        <v>57.29902873212629</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1103,10 +1099,10 @@
         </is>
       </c>
       <c r="T7" s="6" t="n">
-        <v>195.7476275265153</v>
+        <v>196.5718736604782</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>219.1632316817456</v>
+        <v>222.7072554452695</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1118,7 +1114,11 @@
           <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>out of its training distribution (trained on Dutch durations)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TD3_vanilla_extended_ts102</t>
+          <t>ChargeAsFastAsPossible</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -1136,10 +1136,10 @@
         <v>50</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9430164900167692</v>
+        <v>0.9987851874291384</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.9401794483523224</v>
+        <v>0.9983878291241496</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1147,43 +1147,43 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.8939442279484916</v>
+        <v>0.9469199181192218</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.8843675226277575</v>
+        <v>0.9366830129844704</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>24.77490487139432</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>26.17062440362157</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2899262667178346</v>
+        <v>0.0553331249412169</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3039722252875533</v>
+        <v>0.0650806308099252</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>88.78292453917277</v>
+        <v>176.7342879644401</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="T8" s="6" t="n">
-        <v>205.7142412142073</v>
+        <v>226.684671389672</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>240.3750705243245</v>
+        <v>253.1990814461407</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1206,11 +1206,7 @@
           <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>out of its training distribution (trained on Dutch durations)</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1218,7 +1214,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RoundRobin_TransformerCapped</t>
+          <t>RoundRobin</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -1228,10 +1224,10 @@
         <v>50</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9902288640873016</v>
+        <v>0.9558407020336256</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9887627257812498</v>
+        <v>0.9514036786770336</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1239,54 +1235,54 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9388642446523814</v>
+        <v>0.9061713895925836</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.9283104007159336</v>
+        <v>0.8960550921566799</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>3.716609867815905</v>
+        <v>19.02069610815025</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>4.292819768406028</v>
+        <v>20.74325422801842</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.09009963076456649</v>
+        <v>0.2354789053525755</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1020069466982095</v>
+        <v>0.2523482662409649</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>0</v>
+        <v>70.83023173404438</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="T9" s="6" t="n">
-        <v>99.89981312549872</v>
+        <v>195.7476275265153</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>99.89981312549872</v>
+        <v>219.1632316817456</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1298,19 +1294,15 @@
           <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>diagnostic arm added by this brief (budget = transformer rating)</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ChargeAsFastAsPossible</t>
+          <t>RoundRobin_TransformerCapped</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1320,10 +1312,10 @@
         <v>50</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.998769452026644</v>
+        <v>0.9902288640873016</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.9983821644044076</v>
+        <v>0.9887627257812498</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1331,54 +1323,54 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8946179453670902</v>
+        <v>0.9388642446523814</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.8803593387153944</v>
+        <v>0.9283104007159336</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
+        <v>3.716609867815905</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>4.292819768406028</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0.09009963076456649</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0.1020069466982095</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="R10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0.1045610564336793</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0.1182260284236571</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>231.52430923753</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="T10" s="6" t="n">
-        <v>234.0428976327608</v>
+        <v>99.89981312549872</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>240.7059253474302</v>
+        <v>99.89981312549872</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1390,15 +1382,19 @@
           <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>recommended operating strategy (round-robin load management, budget = transformer rating)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RoundRobin</t>
+          <t>MPC_TrackingG2V</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1408,21 +1404,21 @@
         <v>50</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.961418381421186</v>
+        <v>0.8783773184346724</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.9578736719290262</v>
+        <v>0.8667185040309743</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>not met</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.861064238326687</v>
+        <v>0.8326049125989876</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8477055070840712</v>
+        <v>0.8190210301082292</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1430,10 +1426,10 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>16.58173789674412</v>
+        <v>51.68735680957234</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>18.0456701891599</v>
+        <v>56.24391413843966</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1441,10 +1437,10 @@
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2534452572149203</v>
+        <v>0.5436656486331625</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2687521120341635</v>
+        <v>0.5871623899841467</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1452,10 +1448,10 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>95.74541895705715</v>
+        <v>4.0243681557539e-05</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1463,10 +1459,10 @@
         </is>
       </c>
       <c r="T11" s="6" t="n">
-        <v>201.7079028359316</v>
+        <v>100.0005244539645</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>250.7566077161692</v>
+        <v>100.0007151584841</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1482,11 +1478,11 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TD3_vanilla_extended_ts102</t>
+          <t>Optimal_Oracle_Tracking</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1496,10 +1492,10 @@
         <v>50</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9477667650370424</v>
+        <v>0.918266082930887</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9448509894117392</v>
+        <v>0.9134329417931452</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1507,10 +1503,10 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8487504021787542</v>
+        <v>0.8704593637138894</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.8354716912300014</v>
+        <v>0.8611107818588215</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1518,10 +1514,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>22.47779490657648</v>
+        <v>35.59175814146095</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>23.76761475218329</v>
+        <v>37.31664170516319</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1529,10 +1525,10 @@
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3063616364737271</v>
+        <v>0.3920789111798571</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3211074204291139</v>
+        <v>0.4078778139938389</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1540,21 +1536,21 @@
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>122.8260749584879</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>not met</t>
+          <t>met</t>
         </is>
       </c>
       <c r="T12" s="6" t="n">
-        <v>231.5231788662108</v>
+        <v>100.0000780826473</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>253.4947122441825</v>
+        <v>100.0000780826473</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1566,19 +1562,15 @@
           <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>out of its training distribution (trained on Dutch durations)</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RoundRobin_TransformerCapped</t>
+          <t>TD3_vanilla_extended_ts102</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1588,79 +1580,615 @@
         <v>50</v>
       </c>
       <c r="E13" s="4" t="n">
+        <v>0.9430164900167692</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.9401794483523224</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.8939442279484916</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.8843675226277575</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>24.77490487139432</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>26.17062440362157</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.2899262667178346</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0.3039722252875533</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>88.78292453917277</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>205.7142412142073</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>240.3750705243245</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>not evaluable</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>out of its training distribution (trained on Dutch durations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ChargeAsFastAsPossible</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.998769452026644</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.9983821644044076</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.8946179453670902</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.8803593387153944</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.1045610564336793</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0.1182260284236571</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>231.52430923753</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>234.0428976327608</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>240.7059253474302</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>not evaluable</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RoundRobin</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.961418381421186</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.9578736719290262</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.861064238326687</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.8477055070840712</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>16.58173789674412</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>18.0456701891599</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.2534452572149203</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0.2687521120341635</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>95.74541895705715</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>201.7079028359316</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>250.7566077161692</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>not evaluable</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RoundRobin_TransformerCapped</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>0.9891808964582044</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>0.9877796117604616</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>0.8861097316292844</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>0.8715599558252268</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>not met</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>4.21239118762356</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L16" s="5" t="n">
         <v>4.753778547597206</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="n">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>0.1418643511693122</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>0.1569256460152971</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>not met</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>met</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="n">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="n">
         <v>99.89981312549872</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U16" s="6" t="n">
         <v>99.89981312549874</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>not evaluable</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>diagnostic arm added by this brief (budget = transformer rating)</t>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>recommended operating strategy (round-robin load management, budget = transformer rating)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MPC_TrackingG2V</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.8690708382230246</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.8578956106023706</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.7784412903330795</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.7621699333481254</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>56.04202408908193</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>60.43689669485372</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0.606333838932223</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0.6460716315190179</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>7.244938974508401e-05</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>100.0005769132798</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>100.0005769132799</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>not evaluable</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optimal_Oracle_Tracking</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.9211571444246156</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.9169064100800698</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.8248335044983758</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.8121930657865698</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>34.35808678084152</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>35.98010159146766</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0.4132684068110696</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0.4276683914997782</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>100.0000780826473</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>100.0000780826473</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>not evaluable</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TD3_vanilla_extended_ts102</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0.9477667650370424</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.9448509894117392</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>met</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.8487504021787542</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.8354716912300014</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>22.47779490657648</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>23.76761475218329</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0.3063616364737271</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0.3211074204291139</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>122.8260749584879</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>not met</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>231.5231788662108</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>253.4947122441825</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>not evaluable</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>not rerun under DC sessions; the 34-node feeder is out of band with the station idle, and the node_123 result (closure E2) used Dutch durations</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>out of its training distribution (trained on Dutch durations)</t>
         </is>
       </c>
     </row>
